--- a/data_raw/cepes_op_ipc_cepes_serie_historica_agregada_n_indice_1994_2026_03.xlsx
+++ b/data_raw/cepes_op_ipc_cepes_serie_historica_agregada_n_indice_1994_2026_03.xlsx
@@ -4827,13 +4827,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D12A4510-3F3D-4450-A418-C9EF31B22880}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68107752-88CC-41A7-9D8A-49A386D83649}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B599306D-094F-4766-9DAA-A2E0FF703961}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE91FF20-026D-42F9-9A24-43BB22B16632}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{927DE909-43FC-4BE1-8369-E8E5C8E31E81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9745B78A-DB73-47FC-8EC3-ECEF0FAD413C}"/>
 </file>